--- a/Maths/Archive/WegZeit.xlsx
+++ b/Maths/Archive/WegZeit.xlsx
@@ -212,11 +212,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="940226841"/>
-        <c:axId val="850582252"/>
+        <c:axId val="1766604886"/>
+        <c:axId val="957514366"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="940226841"/>
+        <c:axId val="1766604886"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -268,10 +268,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="850582252"/>
+        <c:crossAx val="957514366"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="850582252"/>
+        <c:axId val="957514366"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -346,7 +346,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="940226841"/>
+        <c:crossAx val="1766604886"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -480,11 +480,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1633232112"/>
-        <c:axId val="756822104"/>
+        <c:axId val="1486241207"/>
+        <c:axId val="1350993752"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1633232112"/>
+        <c:axId val="1486241207"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -536,10 +536,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="756822104"/>
+        <c:crossAx val="1350993752"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="756822104"/>
+        <c:axId val="1350993752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -614,7 +614,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1633232112"/>
+        <c:crossAx val="1486241207"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
